--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932885</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118309719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118309785</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932437</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932813</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932896</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932905</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932935</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932599</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932854</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111554297</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,8 +2394,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119319469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126932885</v>
+        <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>83173</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långberget, Jmt</t>
+          <t>Bergmyrbäcken, Bergmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490912</v>
+        <v>492595</v>
       </c>
       <c r="R2" t="n">
-        <v>6942245</v>
+        <v>6945483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,56 +769,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932885</t>
+          <t>https://artportalen.se/Sighting/135791574</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118309719</v>
+        <v>126932885</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stuguberget, Jmt</t>
+          <t>Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490894</v>
+        <v>490912</v>
       </c>
       <c r="R3" t="n">
-        <v>6942132</v>
+        <v>6942245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,13 +892,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118309719</t>
+          <t>https://artportalen.se/Sighting/126932885</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118309785</v>
+        <v>118309719</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -930,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490759</v>
+        <v>490894</v>
       </c>
       <c r="R4" t="n">
-        <v>6942110</v>
+        <v>6942132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,13 +998,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118309785</t>
+          <t>https://artportalen.se/Sighting/118309719</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126932437</v>
+        <v>118309785</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1032,14 +1038,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långberget, Jmt</t>
+          <t>Stuguberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491068</v>
+        <v>490759</v>
       </c>
       <c r="R5" t="n">
-        <v>6942518</v>
+        <v>6942110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,13 +1104,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932437</t>
+          <t>https://artportalen.se/Sighting/118309785</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126932550</v>
+        <v>126932437</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1142,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490858</v>
+        <v>491068</v>
       </c>
       <c r="R6" t="n">
-        <v>6942413</v>
+        <v>6942518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,13 +1210,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932550</t>
+          <t>https://artportalen.se/Sighting/126932437</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126932813</v>
+        <v>126932550</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1248,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490755</v>
+        <v>490858</v>
       </c>
       <c r="R7" t="n">
-        <v>6942170</v>
+        <v>6942413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,13 +1316,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932813</t>
+          <t>https://artportalen.se/Sighting/126932550</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126932896</v>
+        <v>126932813</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1354,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490910</v>
+        <v>490755</v>
       </c>
       <c r="R8" t="n">
-        <v>6942247</v>
+        <v>6942170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,38 +1422,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932896</t>
+          <t>https://artportalen.se/Sighting/126932813</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126932878</v>
+        <v>126932896</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490798</v>
+        <v>490910</v>
       </c>
       <c r="R9" t="n">
-        <v>6942187</v>
+        <v>6942247</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,16 +1528,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932878</t>
+          <t>https://artportalen.se/Sighting/126932896</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126932905</v>
+        <v>126932878</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490964</v>
+        <v>490798</v>
       </c>
       <c r="R10" t="n">
-        <v>6942223</v>
+        <v>6942187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,13 +1634,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932905</t>
+          <t>https://artportalen.se/Sighting/126932878</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126932926</v>
+        <v>126932905</v>
       </c>
       <c r="B11" t="n">
         <v>80432</v>
@@ -1672,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491045</v>
+        <v>490964</v>
       </c>
       <c r="R11" t="n">
-        <v>6942224</v>
+        <v>6942223</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,38 +1740,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932926</t>
+          <t>https://artportalen.se/Sighting/126932905</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126932935</v>
+        <v>126932926</v>
       </c>
       <c r="B12" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491044</v>
+        <v>491045</v>
       </c>
       <c r="R12" t="n">
-        <v>6942225</v>
+        <v>6942224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,48 +1846,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932935</t>
+          <t>https://artportalen.se/Sighting/126932926</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126932599</v>
+        <v>126932935</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1889,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490829</v>
+        <v>491044</v>
       </c>
       <c r="R13" t="n">
-        <v>6942364</v>
+        <v>6942225</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,17 +1928,13 @@
           <t>2025-07-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1955,33 +1952,33 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932599</t>
+          <t>https://artportalen.se/Sighting/126932935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126933327</v>
+        <v>126932599</v>
       </c>
       <c r="B14" t="n">
-        <v>58790</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1990,10 +1987,13 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490868</v>
+        <v>490829</v>
       </c>
       <c r="R14" t="n">
-        <v>6942503</v>
+        <v>6942364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,13 +2039,17 @@
           <t>2025-07-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2063,43 +2067,45 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933327</t>
+          <t>https://artportalen.se/Sighting/126932599</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126932854</v>
+        <v>126933327</v>
       </c>
       <c r="B15" t="n">
-        <v>79917</v>
+        <v>58790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>208245</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2107,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490784</v>
+        <v>490868</v>
       </c>
       <c r="R15" t="n">
-        <v>6942175</v>
+        <v>6942503</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,59 +2175,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932854</t>
+          <t>https://artportalen.se/Sighting/126933327</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111554297</v>
+        <v>126932854</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stuguberget, Gillhov, Hackås, Jmt</t>
+          <t>Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491480</v>
+        <v>490784</v>
       </c>
       <c r="R16" t="n">
-        <v>6940899</v>
+        <v>6942175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,22 +2249,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,33 +2263,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rebecka Johansson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rebecka Johansson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111554297</t>
+          <t>https://artportalen.se/Sighting/126932854</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119319469</v>
+        <v>111554297</v>
       </c>
       <c r="B17" t="n">
-        <v>97986</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,38 +2298,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stuguberget, Jmt</t>
+          <t>Stuguberget, Gillhov, Hackås, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491416</v>
+        <v>491480</v>
       </c>
       <c r="R17" t="n">
-        <v>6941271</v>
+        <v>6940899</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,12 +2360,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,23 +2384,129 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Rebecka Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Rebecka Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111554297</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119319469</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stuguberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>491416</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6941271</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119319469</t>
         </is>
@@ -2418,6 +2530,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 2475-2023 artfynd.xlsx
+++ b/artfynd/S 2475-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791574</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
